--- a/important_mails_2026-06-03.xlsx
+++ b/important_mails_2026-06-03.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -552,21 +552,70 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 3 Jun 2026 02:36:04 +0000</t>
+          <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 06/03/26 14:55 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 604,05.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 3 Jun 2026 02:36:04 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册
@@ -601,39 +650,133 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 3 Jun 2026 15:00:42 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 06/03/26 15:00 CEST, nous avons effectué un virement d’un montant de €
+ 65.85 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 3 Jun 2026 13:54:47 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 06/03/26 13:54 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 137,63.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 13:57:10 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (okvedC6bat)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -653,39 +796,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 08:40:44 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -701,39 +844,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (260520getf)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -758,39 +901,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -806,39 +949,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -863,39 +1006,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -915,39 +1058,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -963,39 +1106,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1015,39 +1158,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1067,39 +1210,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1119,39 +1262,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1171,39 +1314,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1220,39 +1363,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1272,39 +1415,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1324,39 +1467,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1376,39 +1519,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1424,88 +1567,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 27 May 2026 13:35:40 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 05/27/26 13:35 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 308,55.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 12:53:21 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1521,40 +1615,40 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
@@ -1571,40 +1665,40 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -1625,39 +1719,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1675,39 +1769,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1725,39 +1819,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1775,39 +1869,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1825,39 +1919,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -1887,103 +1981,6 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 27 May 2026 17:40:38 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 06/25/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FD8VC559
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-2023103611500356</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 27 May 2026 11:02:38 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
- MARKETPLACE: 1 - PS - APPEAL</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
-Hello,
-Thank you for submitting a second appeal. Your request is still not approved because the issue remains and the product has characteristics of Toys for children.
-We request you take the following action to fulfill the compliance requirements for this product:
-To ensure that your product is not removed from Amazon's US store, you require a test result that confirms your product's compliance with Amazon's Policy. Please initiate a test request for each product to one of the third-party Testing, Inspection, and Certification organizations through Account Health dashboard. See our third-party TIC services help page to learn more: https://sellercentral.amazon.com/help/hub/reference/external/GUTZ2R2DD6P2UMVB .
-For more information on compliance requirements for Toys, please visit: https://sellercentral.amazon.com/help/hub/reference/external/GKJRA3FRPRKVBJJS
-Once testing or verification is requested, please work with the chosen source to provide all requested information to complete testing of your product or verification of your existing test documents. Once the third-party TIC services </t>
-        </is>
-      </c>
-    </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
@@ -3858,7 +3855,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Mon, 25 May 2026 14:39:47 +0000</t>
+          <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3868,11 +3865,60 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 05/27/26 13:35 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 308,55.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 25 May 2026 14:39:47 +0000</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3892,39 +3938,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3944,39 +3990,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3993,39 +4039,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4045,39 +4091,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4097,39 +4143,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -4146,39 +4192,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -4195,39 +4241,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4247,39 +4293,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4303,39 +4349,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4359,39 +4405,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4411,39 +4457,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4463,39 +4509,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4515,39 +4561,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4567,39 +4613,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4615,39 +4661,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4664,39 +4710,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4716,39 +4762,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4765,39 +4811,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4814,39 +4860,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4866,39 +4912,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4918,39 +4964,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4967,40 +5013,137 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 17:40:38 +0000</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 06/25/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FD8VC559
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-2023103611500356</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 11:02:38 +0000</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
+ MARKETPLACE: 1 - PS - APPEAL</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
+Hello,
+Thank you for submitting a second appeal. Your request is still not approved because the issue remains and the product has characteristics of Toys for children.
+We request you take the following action to fulfill the compliance requirements for this product:
+To ensure that your product is not removed from Amazon's US store, you require a test result that confirms your product's compliance with Amazon's Policy. Please initiate a test request for each product to one of the third-party Testing, Inspection, and Certification organizations through Account Health dashboard. See our third-party TIC services help page to learn more: https://sellercentral.amazon.com/help/hub/reference/external/GUTZ2R2DD6P2UMVB .
+For more information on compliance requirements for Toys, please visit: https://sellercentral.amazon.com/help/hub/reference/external/GKJRA3FRPRKVBJJS
+Once testing or verification is requested, please work with the chosen source to provide all requested information to complete testing of your product or verification of your existing test documents. Once the third-party TIC services </t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -5017,40 +5160,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -5067,40 +5210,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -5117,39 +5260,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5169,40 +5312,40 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5218,40 +5361,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -5267,39 +5410,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5318,40 +5461,40 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5367,40 +5510,40 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5414,40 +5557,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5461,40 +5604,40 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -5507,39 +5650,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5559,39 +5702,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -5616,39 +5759,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -5673,40 +5816,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5721,40 +5864,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5768,40 +5911,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5815,41 +5958,41 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -5860,39 +6003,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5911,39 +6054,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5967,39 +6110,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6017,39 +6160,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Tue, 26 May 2026 12:22:30 +0000 (UTC)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>TikTok Shop &lt;tiktokshopseller@shop.tiktok.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>借助这些高潜力商品加速你的业务成长</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  借助这些高潜力商品加速你的业务成长
@@ -6142,39 +6285,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 17:10:44 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6192,39 +6335,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 08:12:17 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Il team di Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Nuova convalida dei numeri di spedizione attiva da oggi</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorniamo i parametri di convalida dei numeri di spedizione per le spedizioni con corrieri non affiliati, includendo controlli relativi alla lunghezza, al formato previsto del corriere e ai requisiti aggiuntivi relativi ai caratteri. Questo ci permetterà di elaborare il tuo inventario più velocemente.
@@ -6235,39 +6378,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 07:52:06 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Disponible desde hoy la nueva validación del número de seguimiento</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Hemos añadido parámetros de validación del número de seguimiento en los envíos con transportistas no asociados para comprobar la longitud, formato previsto del transportista y requisitos de caracteres adicionales y así procesar tu inventario más rápido.
@@ -6279,39 +6422,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6327,39 +6470,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6389,39 +6532,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6436,39 +6579,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6483,39 +6626,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6530,39 +6673,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6577,39 +6720,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6624,39 +6767,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6674,39 +6817,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -6723,39 +6866,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6774,39 +6917,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6821,40 +6964,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6870,39 +7013,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6918,39 +7061,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -6971,39 +7114,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7018,39 +7161,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -7080,39 +7223,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7140,39 +7283,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -7188,39 +7331,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7239,39 +7382,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7293,39 +7436,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7347,39 +7490,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -7398,39 +7541,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7442,39 +7585,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7486,39 +7629,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -7530,39 +7673,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7574,39 +7717,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7618,39 +7761,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7662,39 +7805,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -7713,39 +7856,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -7764,39 +7907,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -7808,39 +7951,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -7852,39 +7995,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -7896,39 +8039,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7940,39 +8083,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -7984,39 +8127,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -8028,39 +8171,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8072,39 +8215,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -8116,39 +8259,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8160,39 +8303,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8204,39 +8347,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -8248,39 +8391,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8292,39 +8435,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8336,40 +8479,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -8388,39 +8531,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8432,39 +8575,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -8476,39 +8619,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8520,39 +8663,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8564,39 +8707,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8608,39 +8751,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8661,39 +8804,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8708,39 +8851,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8759,39 +8902,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8814,39 +8957,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8870,39 +9013,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8926,39 +9069,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8979,39 +9122,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9034,39 +9177,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9090,39 +9233,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9145,40 +9288,40 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -9194,39 +9337,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
